--- a/output/2026-09-16_17_Croazia_Zadarska_Utensilerie_e_Macchine_Utensili.xlsx
+++ b/output/2026-09-16_17_Croazia_Zadarska_Utensilerie_e_Macchine_Utensili.xlsx
@@ -510,7 +510,7 @@
       <c r="F2" s="2" t="inlineStr"/>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Distributore/rivenditore di utensili professionali e attrezzature (rappresentante/importatore Makita, Metabo, Bosch, Dewalt, Stanley, Unior, Knipex, ecc.), incluso DPI e abbigliamento da lavoro. Esistenza confermata dal sito ufficiale e dal listino rivenditori Bosch Professional. Email generica non reperita in fonti pubbliche: campo lasciato vuoto.</t>
+          <t>Distributore/rivenditore di utensili professionali e attrezzature (rappresentante/importatore Makita, Metabo, Bosch, Dewalt, Stanley, Unior, Knipex, ecc.), incluso DPI e abbigliamento da lavoro. Esistenza confermata dal sito ufficiale e dal listino rivenditori Bosch Professional. Email generica non reperita in fonti pubbliche: campo lasciato vuoto. [DUPLICATO — vedi anche: 2026-09-16_17_Croazia_Zadarska_Metalworking_Lavorazioni_Metalliche.xlsx]</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Distributore di utensili, ferramenta, prodotti in metallo, materiale elettrico e attrezzatura nautica. Attiva dal 1995, 19 dipendenti. Esistenza e attivita confermate tramite fininfo.hr, companywall.hr e sito ufficiale.</t>
+          <t>Distributore di utensili, ferramenta, prodotti in metallo, materiale elettrico e attrezzatura nautica. Attiva dal 1995, 19 dipendenti. Esistenza e attivita confermate tramite fininfo.hr, companywall.hr e sito ufficiale. [DUPLICATO — vedi anche: 2026-09-16_17_Croazia_Zadarska_Metalworking_Lavorazioni_Metalliche.xlsx]</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">

--- a/output/2026-09-16_17_Croazia_Zadarska_Utensilerie_e_Macchine_Utensili.xlsx
+++ b/output/2026-09-16_17_Croazia_Zadarska_Utensilerie_e_Macchine_Utensili.xlsx
@@ -599,7 +599,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (21/09/2026)</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (21/09/2026)</t>
         </is>
       </c>
     </row>

--- a/output/2026-09-16_17_Croazia_Zadarska_Utensilerie_e_Macchine_Utensili.xlsx
+++ b/output/2026-09-16_17_Croazia_Zadarska_Utensilerie_e_Macchine_Utensili.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Centro all'ingrosso B2B Würth confermato in Ulica dr. Franje Tuđmana 24 (na Relji), 23000 Zadar. Fonti online rilevano anche un telefono (023 551 259) e un'email (shop_zadar1@wuerth.com.hr) alternativi per lo stesso centro: si consiglia una verifica diretta del recapito attualmente attivo.</t>
+          <t>Centro all'ingrosso B2B Würth confermato in Ulica dr. Franje Tuđmana 24 (na Relji), 23000 Zadar. Fonti online rilevano anche un telefono (023 551 259) e un'email (shop_zadar1@wuerth.com.hr) alternativi per lo stesso centro: si consiglia una verifica diretta del recapito attualmente attivo. [DUPLICATO — vedi anche: 2026-09-16_17_Croazia_Zadarska_Metalworking_Lavorazioni_Metalliche.xlsx]</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
